--- a/astro-site/public/dl/kit-tareas-heladeria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/03-tareas-manager.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tareas Diarias" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tareas Semanales" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tareas Mensuales" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Diarias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Semanales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Mensuales" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tareas Diarias'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tareas Semanales'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Tareas Mensuales'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -163,63 +172,74 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -579,15 +599,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -595,6 +616,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -623,9 +645,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -654,8 +674,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -664,18 +701,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -692,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -812,6 +850,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -932,6 +971,7 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -1051,6 +1091,26 @@
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>COUNTIF(E6:E23,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>COUNTIF(B6:B23,"?*")</f>
+        <v>14.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
@@ -1076,12 +1136,26 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1090,18 +1164,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1118,6 +1192,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1238,6 +1313,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1358,6 +1434,7 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -1458,6 +1535,26 @@
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>COUNTIF(E6:E22,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>COUNTIF(B6:B22,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
@@ -1483,12 +1580,26 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1497,18 +1608,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1525,6 +1636,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1645,6 +1757,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1746,6 +1859,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1903,6 +2017,26 @@
       <c r="E24" s="12" t="n"/>
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C25">
+        <f>COUNTIF(E6:E24,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E25">
+        <f>COUNTIF(B6:B24,"?*")</f>
+        <v>15.0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
@@ -1928,11 +2062,25 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23 E24" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-heladeria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/03-tareas-manager.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -676,9 +676,38 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Registro de jornada:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ El registro horario diario es obligatorio para toda la plantilla desde el RD-ley 8/2019, temporeros incluidos: se cierra y se firma cada día y se archiva cada mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ Los registros se conservan 4 años y tienen que estar a disposición de la Inspección de Trabajo y de los representantes de los trabajadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -703,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -837,7 +866,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Comprobar mezclas en maduración listas para manteccar</t>
+          <t>Comprobar mezclas en maduración listas para mantecar</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -971,77 +1000,77 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Cerrar y validar el registro diario de jornada del equipo (entradas, salidas y descansos) y que cada persona lo firme el mismo día: es obligatorio desde el RD-ley 8/2019, también para el refuerzo de temporada</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Servicio y calidad</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Supervisar presentación de vitrina (atractivo visual, orden)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Vitrina</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Verificar rotación de sabores en vitrina (FIFO)</t>
+          <t>Supervisar presentación de vitrina (atractivo visual, orden)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -1056,16 +1085,16 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Probar sabor del día / nueva receta si procede</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Verificar rotación de sabores en vitrina (FIFO)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D22" s="11" t="n"/>
@@ -1075,16 +1104,16 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Atender reseñas online y responder comentarios</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Probar sabor del día / nueva receta si procede</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D23" s="11" t="n"/>
@@ -1093,34 +1122,53 @@
       <c r="G23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="inlineStr">
+      <c r="A24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Atender reseñas online y responder comentarios</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C24">
-        <f>COUNTIF(E6:E23,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25">
+        <f>COUNTIFS(B6:B24,"?*",E6:E24,"✓")-COUNTIFS(B6:B24,"Tarea",E6:E24,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E24">
-        <f>COUNTIF(B6:B23,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E25">
+        <f>COUNTIF(B6:B24,"?*")-COUNTIF(B6:B24,"Tarea")-COUNTIF(E6:E24,"N/A")</f>
+        <v>13.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1130,20 +1178,20 @@
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G23">
+  <conditionalFormatting sqref="A6:G24">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1543,8 +1591,8 @@
         </is>
       </c>
       <c r="C23">
-        <f>COUNTIF(E6:E22,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B22,"?*",E6:E22,"✓")-COUNTIFS(B6:B22,"Tarea",E6:E22,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1552,8 +1600,8 @@
         </is>
       </c>
       <c r="E23">
-        <f>COUNTIF(B6:B22,"?*")</f>
-        <v>13.0</v>
+        <f>COUNTIF(B6:B22,"?*")-COUNTIF(B6:B22,"Tarea")-COUNTIF(E6:E22,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
     <row r="24">
@@ -1586,8 +1634,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1610,7 +1658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1846,7 +1894,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Sesión de formación: nuevas recetas, técnicas, atención al cliente</t>
+          <t>Archivar los registros de jornada del mes y conservarlos 4 años a disposición de la Inspección de Trabajo y de los representantes de los trabajadores</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -1859,82 +1907,82 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Sesión de formación: nuevas recetas, técnicas, atención al cliente</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Producto y mantenimiento</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Mantenimiento preventivo de maquinaria (revisar juntas, filtros)</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Planificar carta estacional del mes siguiente</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Mantenimiento preventivo de maquinaria (revisar juntas, filtros)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D20" s="11" t="n"/>
@@ -1944,11 +1992,11 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Actualizar fichas técnicas de sabores si hay cambios</t>
+          <t>Planificar carta estacional del mes siguiente</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -1963,11 +2011,11 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Revisar y responder reseñas online del mes</t>
+          <t>Actualizar fichas técnicas de sabores si hay cambios</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -1982,11 +2030,11 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Evaluar proveedores: calidad, precio, cumplimiento</t>
+          <t>Revisar y responder reseñas online del mes</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -2001,11 +2049,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Revisar documentación APPCC y registros del mes</t>
+          <t>Evaluar proveedores: calidad, precio, cumplimiento</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2019,34 +2067,53 @@
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="A25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Revisar documentación APPCC y registros del mes</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C25">
-        <f>COUNTIF(E6:E24,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26">
+        <f>COUNTIFS(B6:B25,"?*",E6:E25,"✓")-COUNTIFS(B6:B25,"Tarea",E6:E25,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E25">
-        <f>COUNTIF(B6:B24,"?*")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E26">
+        <f>COUNTIF(B6:B25,"?*")-COUNTIF(B6:B25,"Tarea")-COUNTIF(E6:E25,"N/A")</f>
+        <v>14.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -2055,21 +2122,21 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G24">
+  <conditionalFormatting sqref="A6:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-heladeria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/03-tareas-manager.xlsx
@@ -1178,10 +1178,10 @@
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G24">
@@ -2125,8 +2125,8 @@
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G25">
